--- a/Rezepte/Pistazien-Schoko Törtchen.xlsx
+++ b/Rezepte/Pistazien-Schoko Törtchen.xlsx
@@ -17,17 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,15 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C52"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Pistazien-Schoko Törtchen</t>
         </is>
@@ -435,206 +427,242 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Übernacht Vorbereitung:</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Brownieboden, Pistazienganache</t>
+          <t>Maximal gleichzeitig herstellbare Menge</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>60x</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brownieboden (Mittwoch)</t>
+          <t>Haltbarkeit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4 Tage (Kühlung) / 3 Monate (Froster)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zutat</t>
+          <t>Hinweis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Menge</t>
+          <t>Vortag: Boden 15 Min backen + über Nacht auskühlen | Pistazienganache über Nacht kühlen | Pistazienkern 1h Schockfroster | Törtchen in Form 2h Schockfroster | Fertig 4h kühlen</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zartbitterkuvertüre</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>200</v>
+          <t>Brownieboden (pro Stück)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Butter</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>150</v>
+          <t>Zutat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Menge</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zucker</t>
+          <t>Callebaut dark</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>180</v>
+        <v>12.667</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vollei</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mehl</t>
+          <t>Vollei</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>11.333</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kakaopulver</t>
+          <t>Zucker</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Salz</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.067</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pistazienganache (Mittwoch)</t>
-        </is>
+          <t>Weizenmehl</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3.667</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zutat</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Menge</t>
+          <t>Pistazienkern (pro Stück)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sahne</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>200</v>
+          <t>Zutat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Menge</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Weiße Kuvertüre</t>
+          <t>Sahne</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300</v>
+        <v>3.533</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pistazienpaste</t>
+          <t>Callebaut white</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>5.333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Invertzucker</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.333</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pistazienkern (Donnerstag)</t>
-        </is>
+          <t>Pistazienpaste</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zutat</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Menge</t>
+          <t>Pistazienganache (pro Stück)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sahne</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>150</v>
+          <t>Zutat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Menge</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Weiße Kuvertüre</t>
+          <t>Callebaut white</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>150</v>
+        <v>3.333</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pistazienpaste</t>
+          <t>Gelatine</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gelatine</t>
+          <t>Sahne</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pistazienpaste</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Schoko-Mousse (Donnerstag)</t>
+          <t>Schoko Mousse (pro Stück)</t>
         </is>
       </c>
     </row>
@@ -653,173 +681,71 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zartbitterkuvertüre</t>
+          <t>Milch</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>350</v>
+        <v>5.333</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sahne (1)</t>
+          <t>Zucker</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100</v>
+        <v>1.333</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sahne (2)</t>
+          <t>Gelatine</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>400</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Glukosesirup</t>
+          <t>Callebaut dark</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Schlagsahne</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>23.333</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Maximal herzustellende Menge:</t>
-        </is>
+          <t>Zeitaufwand aktiv</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>60 Stück (1 Grundrezept = 60 Mousseformen)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Herstellung:</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Mittwoch: Brownieboden backen, auskühlen lassen</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Mittwoch: Pistazienganache herstellen, kalt stellen</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Donnerstag: Kern herstellen, schockfrosten (min. 1h)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Donnerstag: Brownieboden ausstechen</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Donnerstag: Schoko-Mousse herstellen</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Donnerstag: Mousse in Formen, Kern eindrücken, Boden auflegen</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Donnerstag: Schockfrosten (min. 2h)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Donnerstag: Aus Form lösen, Pistazienganache aufdressieren</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Haltbarkeit:</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Kühlung</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3 Tage</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Froster</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3 Monate</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Zeitaufwand aktiv:</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Zeitaufwand passiv:</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>180 min</t>
-        </is>
+          <t>Zeitaufwand passiv</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
